--- a/medical_surveys_questionnaires/035_self_report_measures_assessment_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/035_self_report_measures_assessment_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>self_report_measures_assessment_form_page</t>
+          <t>survey_purpose</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>What is the purpose of this survey?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>medical_surveys_questionnaires</t>
+          <t>survey_author</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is this survey used for?</t>
+          <t>Who is the author of this survey?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medical_surveys_questionnaires_1</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>This is a survey to collect information about</t>
+          <t>What is the name of your survey?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>medical_surveys_questionnaires_2</t>
+          <t>survey_description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>about various health related topics</t>
+          <t>What is a brief description of your survey?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_surveys_questionnaires_3</t>
+          <t>survey_frequency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>to understand human behavior better</t>
+          <t>How often will this survey be administered?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>survey_duration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the name of your survey?</t>
+          <t>How long will this survey take to complete?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>survey_description</t>
+          <t>survey_instruments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is a brief description of your survey?</t>
+          <t>What instruments will you use to administer this survey?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_surveys_questionnaires_4</t>
+          <t>survey_scope</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>This is a survey to collect information about</t>
+          <t>What is the scope of this survey?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,64 +704,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_surveys_questionnaires_5</t>
+          <t>survey_version</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>your responses will be kept confidential</t>
+          <t>What version is this survey?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>survey_instrument_version</t>
+          <t>survey_due_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What version is this survey?</t>
+          <t>When is this survey due?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>survey_author</t>
+          <t>survey_due_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Who is the author of this survey?</t>
+          <t>At what time will this survey be due?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>survey_contact</t>
+          <t>survey_purpose_details</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Who do you contact for further information?</t>
+          <t>Please provide more details about the purpose of this survey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,294 +796,64 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_surveys_questionnaires_6</t>
+          <t>survey_author_details</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>This is a survey to collect information about</t>
+          <t>Please provide more details about the author of this survey</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>survey_date</t>
+          <t>survey_instruments_details</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>When is this survey due?</t>
+          <t>Please provide more details about the instruments used in this survey</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>survey_time</t>
+          <t>survey_scope_details</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>At what time will this survey be due?</t>
+          <t>Please provide more details about the scope of this survey</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>medical_surveys_questionnaires_7</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>This is a survey to collect information about</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>survey_frequency</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How often will this survey be administered?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>medical_surveys_questionnaires_8</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>This is a survey to collect information about</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>survey_duration</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How long will this survey take to complete?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>survey_instruments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What instruments will you use to administer this survey?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medical_surveys_questionnaires_9</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>This is a survey to collect information about</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>survey_purpose</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the purpose of this survey?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>medical_surveys_questionnaires_10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>This is a survey to collect information about</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>survey_scope</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is the scope of this survey?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>medical_surveys_questionnaires_11</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>This is a survey to collect information about</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option_0':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option_0': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1148,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option_1':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option_1': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1165,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option_2':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option_2': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1182,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option_3':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option_3': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1199,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option_4':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option_4': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
